--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0003T0006Z000C1N42_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0003T0006Z000C1N42_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.7959363568805</v>
+        <v>4.029339657993082</v>
       </c>
       <c r="D2" t="n">
-        <v>25.4558562021199</v>
+        <v>4.136576632844484</v>
       </c>
       <c r="E2" t="n">
-        <v>10.23330172908066</v>
+        <v>1.662911530975607</v>
       </c>
       <c r="F2" t="n">
-        <v>10.58882450399475</v>
+        <v>1.720683981899148</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.12988793130103</v>
+        <v>3.758606788836417</v>
       </c>
       <c r="D3" t="n">
-        <v>23.12014916065274</v>
+        <v>3.75702423860607</v>
       </c>
       <c r="E3" t="n">
-        <v>10.23330172908066</v>
+        <v>1.662911530975607</v>
       </c>
       <c r="F3" t="n">
-        <v>10.58882450399475</v>
+        <v>1.720683981899148</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.88305689958281</v>
+        <v>2.255996746182206</v>
       </c>
       <c r="D4" t="n">
-        <v>15.23905840894972</v>
+        <v>2.47634699145433</v>
       </c>
       <c r="E4" t="n">
-        <v>10.23330172908066</v>
+        <v>1.662911530975607</v>
       </c>
       <c r="F4" t="n">
-        <v>10.58882450399475</v>
+        <v>1.720683981899148</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.35930381945004</v>
+        <v>2.983386870660631</v>
       </c>
       <c r="D5" t="n">
-        <v>19.88299585422058</v>
+        <v>3.230986826310845</v>
       </c>
       <c r="E5" t="n">
-        <v>10.23330172908066</v>
+        <v>1.662911530975607</v>
       </c>
       <c r="F5" t="n">
-        <v>10.58882450399475</v>
+        <v>1.720683981899148</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>18.41814043911268</v>
+        <v>2.992947821355811</v>
       </c>
       <c r="D6" t="n">
-        <v>12.573211224499</v>
+        <v>2.043146823981088</v>
       </c>
       <c r="E6" t="n">
-        <v>10.23330172908066</v>
+        <v>1.662911530975607</v>
       </c>
       <c r="F6" t="n">
-        <v>10.58882450399475</v>
+        <v>1.720683981899148</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.70046667520938</v>
+        <v>5.151325834721525</v>
       </c>
       <c r="D7" t="n">
-        <v>30.58486650099601</v>
+        <v>4.970040806411852</v>
       </c>
       <c r="E7" t="n">
-        <v>10.23330172908066</v>
+        <v>1.662911530975607</v>
       </c>
       <c r="F7" t="n">
-        <v>10.58882450399475</v>
+        <v>1.720683981899148</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>7.200621460902559</v>
+        <v>1.170100987396666</v>
       </c>
       <c r="D8" t="n">
-        <v>3.029391602011518</v>
+        <v>0.4922761353268718</v>
       </c>
       <c r="E8" t="n">
-        <v>10.23330172908066</v>
+        <v>1.662911530975607</v>
       </c>
       <c r="F8" t="n">
-        <v>10.58882450399475</v>
+        <v>1.720683981899148</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>10.73654007830671</v>
+        <v>1.74468776272484</v>
       </c>
       <c r="D9" t="n">
-        <v>12.35846748116489</v>
+        <v>2.008250965689294</v>
       </c>
       <c r="E9" t="n">
-        <v>10.23330172908066</v>
+        <v>1.662911530975607</v>
       </c>
       <c r="F9" t="n">
-        <v>10.58882450399475</v>
+        <v>1.720683981899148</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>9.159819615626731</v>
+        <v>1.488470687539344</v>
       </c>
       <c r="D10" t="n">
-        <v>20.33838735003344</v>
+        <v>3.304987944380434</v>
       </c>
       <c r="E10" t="n">
-        <v>10.23330172908066</v>
+        <v>1.662911530975607</v>
       </c>
       <c r="F10" t="n">
-        <v>10.58882450399475</v>
+        <v>1.720683981899148</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>16.55584365514531</v>
+        <v>2.690324593961114</v>
       </c>
       <c r="D11" t="n">
-        <v>19.55325660469758</v>
+        <v>3.177404198263357</v>
       </c>
       <c r="E11" t="n">
-        <v>10.23330172908066</v>
+        <v>1.662911530975607</v>
       </c>
       <c r="F11" t="n">
-        <v>10.58882450399475</v>
+        <v>1.720683981899148</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>31.13316819186279</v>
+        <v>5.059139831177703</v>
       </c>
       <c r="D12" t="n">
-        <v>32.23174001350513</v>
+        <v>5.237657752194584</v>
       </c>
       <c r="E12" t="n">
-        <v>10.23330172908066</v>
+        <v>1.662911530975607</v>
       </c>
       <c r="F12" t="n">
-        <v>10.58882450399475</v>
+        <v>1.720683981899148</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>31.94015268921762</v>
+        <v>5.190274811997864</v>
       </c>
       <c r="D13" t="n">
-        <v>36.08340298242472</v>
+        <v>5.863552984644016</v>
       </c>
       <c r="E13" t="n">
-        <v>10.23330172908066</v>
+        <v>1.662911530975607</v>
       </c>
       <c r="F13" t="n">
-        <v>10.58882450399475</v>
+        <v>1.720683981899148</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>43.12416719266641</v>
+        <v>7.007677168808291</v>
       </c>
       <c r="D14" t="n">
-        <v>43.72956094988486</v>
+        <v>7.106053654356289</v>
       </c>
       <c r="E14" t="n">
-        <v>10.23330172908066</v>
+        <v>1.662911530975607</v>
       </c>
       <c r="F14" t="n">
-        <v>10.58882450399475</v>
+        <v>1.720683981899148</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
